--- a/Egyptian_Governates.xlsx
+++ b/Egyptian_Governates.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Egyptian Governates" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Egyptian Governates &amp; Cities" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,9 +28,17 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -43,8 +51,14 @@
         <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,17 +66,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -429,10 +452,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,6 +465,11 @@
           <t>Governate</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cities</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -448,6 +477,11 @@
           <t>Alexandria</t>
         </is>
       </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Alexandria, Borg El Arab, Montaza, Sidi Bishr</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -455,6 +489,11 @@
           <t>Aswan</t>
         </is>
       </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Aswan, Abu Simbel, Kom Ombo, Edfu, Daraw</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -462,6 +501,11 @@
           <t>Asyut</t>
         </is>
       </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Asyut, Manfalut, Dayrut, Abydos, Sohag</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -469,6 +513,11 @@
           <t>Beheira</t>
         </is>
       </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Damanhur, Kafr El Dawwar, Rosetta, Edku, Abu Hummus</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -476,6 +525,11 @@
           <t>Beni Suef</t>
         </is>
       </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Beni Suef, El Fashn, Samasta, Ibshaway, Nasser</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -483,6 +537,11 @@
           <t>Cairo</t>
         </is>
       </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Cairo, Heliopolis, Nasr City, New Cairo, 6th of October City</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -490,6 +549,11 @@
           <t>Dakahlia</t>
         </is>
       </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Mansoura, Talkha, Aga, Mit Ghamr, Sherbin</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -497,6 +561,11 @@
           <t>Damietta</t>
         </is>
       </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Damietta, New Damietta, Port Fuad, Kafr El Sheikh</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -504,6 +573,11 @@
           <t>Faiyum</t>
         </is>
       </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Faiyum, Siwa, Karanis, Ibshaway, Sinnuris</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -511,6 +585,11 @@
           <t>Gharbia</t>
         </is>
       </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Tanta, Kafr El Zayat, Samannud, Zifta, Mahalla</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -518,6 +597,11 @@
           <t>Giza</t>
         </is>
       </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Giza, 6th of October, Helwan, Badrasheen, Dahshur</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -525,6 +609,11 @@
           <t>Helwan</t>
         </is>
       </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Helwan, Maadi, Wadi Hof, Ain Sukhna, Tura</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -532,6 +621,11 @@
           <t>Ismailia</t>
         </is>
       </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Ismailia, Port Said, Suez, El Qantara, Fayid</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -539,6 +633,11 @@
           <t>Kafr El Sheikh</t>
         </is>
       </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Kafr El Sheikh, Dessouk, Balamun, El Riyad, Sidi Salem</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -546,6 +645,11 @@
           <t>Kalyubia</t>
         </is>
       </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Benha, Qalyub, Shubra El Khaimah, Helwan, 10th of Ramadan</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -553,6 +657,11 @@
           <t>Luxor</t>
         </is>
       </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Luxor, Karnak, Thebes, West Bank, Valley of the Kings</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -560,6 +669,11 @@
           <t>Matruh</t>
         </is>
       </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Matruh, Siwa, Salloum, Sidi Barrani, Alamein</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -567,6 +681,11 @@
           <t>Minya</t>
         </is>
       </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Minya, Samalut, Beni Hassan, Hermopolis, El Minya</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -574,6 +693,11 @@
           <t>Monufia</t>
         </is>
       </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Shebin El Kom, Menouf, Shibin El Qanater, Sadat City, Bagour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -581,6 +705,11 @@
           <t>New Valley</t>
         </is>
       </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Kharga, Dakhla, Mut, Balat, Farafra</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -588,6 +717,11 @@
           <t>North Sinai</t>
         </is>
       </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Arish, Rafah, Sheikh Zuwaid, Bir El Abd, El Qantara</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -595,6 +729,11 @@
           <t>Port Said</t>
         </is>
       </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Port Said, Port Fuad, El Gamil, El Zohour, PORT SAID</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -602,6 +741,11 @@
           <t>Qena</t>
         </is>
       </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Qena, Nag Hammadi, Dendera, Abydos, Coptos</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -609,6 +753,11 @@
           <t>Red Sea</t>
         </is>
       </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Hurghada, Safaga, Quseir, Marsa Alam, Shalateen</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -616,6 +765,11 @@
           <t>Sharqia</t>
         </is>
       </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Zagazig, Ismailia, Belbeis, 10th of Ramadan, Maadi</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -623,11 +777,21 @@
           <t>South Sinai</t>
         </is>
       </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Sharm El Sheikh, Dahab, Nuweiba, Saint Catherine, Taba</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Suez</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Suez, Ain Sukhna, Ataqa, El Ganayen, Fayid</t>
         </is>
       </c>
     </row>

--- a/Egyptian_Governates.xlsx
+++ b/Egyptian_Governates.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Egyptian Governates &amp; Cities" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="المحافظات والمدن" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,15 +26,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -58,7 +61,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -72,21 +75,44 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,350 +478,2675 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Governate</t>
+          <t>المدينة</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Cities</t>
+          <t>المحافظة</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>أسوان</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Alexandria, Borg El Arab, Montaza, Sidi Bishr</t>
+          <t>أسوان</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Aswan</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Aswan, Abu Simbel, Kom Ombo, Edfu, Daraw</t>
-        </is>
-      </c>
+          <t>أبو سمبل</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Asyut</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Asyut, Manfalut, Dayrut, Abydos, Sohag</t>
-        </is>
-      </c>
+          <t>كوم أمبو</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Beheira</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Damanhur, Kafr El Dawwar, Rosetta, Edku, Abu Hummus</t>
-        </is>
-      </c>
+          <t>إدفو</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Beni Suef</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Beni Suef, El Fashn, Samasta, Ibshaway, Nasser</t>
-        </is>
-      </c>
+          <t>داراو</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Cairo, Heliopolis, Nasr City, New Cairo, 6th of October City</t>
-        </is>
-      </c>
+          <t>نصر الساحل</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Dakahlia</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Mansoura, Talkha, Aga, Mit Ghamr, Sherbin</t>
-        </is>
-      </c>
+          <t>الشيخ علي</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Damietta</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Damietta, New Damietta, Port Fuad, Kafr El Sheikh</t>
-        </is>
-      </c>
+          <t>توشكا</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Faiyum</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Faiyum, Siwa, Karanis, Ibshaway, Sinnuris</t>
-        </is>
-      </c>
+          <t>الحمراء</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Gharbia</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Tanta, Kafr El Zayat, Samannud, Zifta, Mahalla</t>
-        </is>
-      </c>
+          <t>النوبة</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Giza</t>
+          <t>أسيوط</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Giza, 6th of October, Helwan, Badrasheen, Dahshur</t>
+          <t>أسيوط</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Helwan</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Helwan, Maadi, Wadi Hof, Ain Sukhna, Tura</t>
-        </is>
-      </c>
+          <t>منفلوط</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Ismailia</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Ismailia, Port Said, Suez, El Qantara, Fayid</t>
-        </is>
-      </c>
+          <t>ديروط</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Kafr El Sheikh</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Kafr El Sheikh, Dessouk, Balamun, El Riyad, Sidi Salem</t>
-        </is>
-      </c>
+          <t>الوقف</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Kalyubia</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Benha, Qalyub, Shubra El Khaimah, Helwan, 10th of Ramadan</t>
-        </is>
-      </c>
+          <t>أبيدوس</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Luxor</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Luxor, Karnak, Thebes, West Bank, Valley of the Kings</t>
-        </is>
-      </c>
+          <t>سوهاج</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Matruh</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Matruh, Siwa, Salloum, Sidi Barrani, Alamein</t>
-        </is>
-      </c>
+          <t>البدارى</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Minya</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Minya, Samalut, Beni Hassan, Hermopolis, El Minya</t>
-        </is>
-      </c>
+          <t>فلنج</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Monufia</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Shebin El Kom, Menouf, Shibin El Qanater, Sadat City, Bagour</t>
-        </is>
-      </c>
+          <t>أراب العوامر</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>New Valley</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Kharga, Dakhla, Mut, Balat, Farafra</t>
-        </is>
-      </c>
+          <t>الغنايم</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>North Sinai</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Arish, Rafah, Sheikh Zuwaid, Bir El Abd, El Qantara</t>
-        </is>
-      </c>
+          <t>الفيوم الجديدة</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Port Said</t>
+          <t>الأقصر</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Port Said, Port Fuad, El Gamil, El Zohour, PORT SAID</t>
+          <t>الأقصر</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Qena</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Qena, Nag Hammadi, Dendera, Abydos, Coptos</t>
-        </is>
-      </c>
+          <t>الكرنك</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Red Sea</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Hurghada, Safaga, Quseir, Marsa Alam, Shalateen</t>
-        </is>
-      </c>
+          <t>البر الغربي</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Sharqia</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Zagazig, Ismailia, Belbeis, 10th of Ramadan, Maadi</t>
-        </is>
-      </c>
+          <t>الضفة الغربية</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>South Sinai</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Sharm El Sheikh, Dahab, Nuweiba, Saint Catherine, Taba</t>
-        </is>
-      </c>
+          <t>وادي الملوك</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Suez</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Suez, Ain Sukhna, Ataqa, El Ganayen, Fayid</t>
-        </is>
-      </c>
+          <t>معبد الدير البحري</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>مدينة الأقصر</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>إسنا</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>أرمنت</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>الإسكندرية</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>الإسكندرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>برج العرب</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>مونتازا</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>سيدي بشر</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>أبي قير</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>الدخيلة</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>كوم الدكة</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ستانلي</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>الشاطبي</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>رشدي</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>الرملة</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>الإبراهيمية</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>القنطرة</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>كفر عبده</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>الحمام</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>مارينا</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>عمومية</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>ضواحي</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>الإسماعيلية</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>الإسماعيلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>بورسعيد</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>السويس</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>القنطرة غرب</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>القنطرة شرق</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>فايد</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>تل الكبير</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>الشلوفة</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>الدفرسوار</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>الغردقة</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>البحر الأحمر</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>سفاجة</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>القصير</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>مرسى علم</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>شلاتين</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>حلايب</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>أبو رماد</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>قصير الجديدة</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>رأس غارب</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>دهب</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>دمنهور</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>البحيرة</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>كفر الدوار</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>رشيد</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>إدكو</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>أبو حمص</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>كوم حمادة</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>شبراخيت</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>نوقة</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>الحامول</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>شرقية</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>الدلنجات</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>إيتاي البارود</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>بسيون</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>سنجور</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>الجيزة</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>الجيزة</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>مدينة 6 أكتوبر</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>حلوان</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>البدرشين</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>دهشور</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>أبو رواش</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>الوراق</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>الساحل</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>الكيت كات</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>الهرم</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>إمبابة</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>العمرانية</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>الحوامدية</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>أطفيح</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>بني سويف الجديدة</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>المنيل</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>المنصورة</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>الدقهلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>طلخا</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>آجا</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>مِت غمر</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>شربين</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>بلقاس</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>جمصة</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>السنبلاوين</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>ميت سلسيل</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>أجا</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>المتينة</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>منية النصر</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>كفر سعد</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>السويس</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>السويس</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>عين سخنة</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>عطاقة</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>الجنايين</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>فايد</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>ناقصة</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>القصير</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>الدفرسوار</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>الزقازيق</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>الشرقية</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>الإسماعيلية</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>بلبيس</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>مدينة 10 رمضان</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>المعادي</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>فاقوس</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>القنايات</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>أبو حماد</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>الجزيرة</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>ههيا</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>درب السلام</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>الصالحية</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>طنطا</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>الغربية</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>كفر الزيات</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>سمنود</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>زفتا</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>المحلة الكبرى</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>قطور</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>سان الحجر</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>بسيون</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>الدلتا الجديدة</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>الفيوم</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>الفيوم</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>سيوه</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>القرين</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>إبشواي</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>سنوريس</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>طامية</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>اطسا</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>يوسف الصديق</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>العدوة</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>آثار</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>القاهرة</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>القاهرة</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>مدينة نصر</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>مصر الجديدة</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>الزمالك</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>الجيزة</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>العبّاسية</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>مدينة 6 أكتوبر</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>مدينة الشروق</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>مدينة بدر</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>مدينة 15 مايو</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>المعادي</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>حلوان</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>المقطم</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>القاهرة الجديدة</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>الشيخ زايد</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>الرحاب</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>الحي العاشر</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>المنيل</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>الدقي</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>الجيزة</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>الموسكي</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>الفجالة</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>باب الشعرية</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>الساحل</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>المطرية</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>عين شمس</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>الزيتون</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>وسيط</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>المنصورية</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>الدراسة</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>درب الجنينة</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>الشرابية</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>النزهة</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>الرويسي</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>قصر النيل</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>الفسطاط</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>الرحاب</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>بنها</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>القليوبية</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>قليوب</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>شبرا الخيمة</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>الخانكة</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>رمسيس</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>مدينة 10 رمضان</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>الشيخ زايد</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>القناطر الخيرية</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>قها</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>الدقهلية</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>الجيزة</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>أوسيم</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>طره</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>الخصوص</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>القنطرة</t>
+        </is>
+      </c>
+      <c r="B203" s="5" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>شبين الكوم</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>المنوفية</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>منوف</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>شبين القناطر</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>مدينة السادات</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>باقور</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>تلا</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>قويسنا</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>أشمون</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>البرجايه</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>بركة السبع</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>منوف الجديدة</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>كفر عبده</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>سمالوط</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>بني حسن</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>هرموبوليس</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>ملوي</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>العدوة</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>ديروط الشريف</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>أبوقرقاص</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>الفشن</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>بني مازن</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>العدوة</t>
+        </is>
+      </c>
+      <c r="B226" s="5" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>الخارجة</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>الوادي الجديد</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>الداخلة</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>موط</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>بلاط</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>فرافرة</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>باريس</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>القصر</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>تينيدة</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>دوش</t>
+        </is>
+      </c>
+      <c r="B235" s="5" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>بني سويف</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>بني سويف</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>الفشن</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>ساماستا</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>إبشواي</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>الجندية</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>ناصر</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>هواره</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>موشية</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>نصار البحرية</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>أحمد حمزة</t>
+        </is>
+      </c>
+      <c r="B245" s="5" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>بورسعيد</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>بورسعيد</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>بورفؤاد</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>الجميل</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>الزهور</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>بورسعيد</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>الكنتاوي</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>الضواحي</t>
+        </is>
+      </c>
+      <c r="B252" s="5" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>شرم الشيخ</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>جنوب سيناء</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>داهب</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>نويبع</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>سانت كاترين</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>طابا</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>رأس محمد</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>أم سيد</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>مدينة شرم الشيخ</t>
+        </is>
+      </c>
+      <c r="B260" s="5" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>حلوان</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>حلوان</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>المعادي</t>
+        </is>
+      </c>
+      <c r="B262" s="4" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>واحة الفيوم</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>وادي حوف</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>عين سخنة</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>الطور</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>الزيتون</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>المقطم</t>
+        </is>
+      </c>
+      <c r="B268" s="5" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>دمياط</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>دمياط</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>دمياط الجديدة</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>بورت فؤاد</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>كفر البطة</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>كفر سعيد</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>الروضة</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>الزرقا</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>فارسكور</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>رومانية</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>العريش</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>شمال سيناء</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>رفح</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>الشيخ زويد</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>بئر العبد</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>القنطرة، سيناء</t>
+        </is>
+      </c>
+      <c r="B282" s="4" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>نخل</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>جديدة، حسنة</t>
+        </is>
+      </c>
+      <c r="B284" s="4" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>دهب الشرقية</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>طابا</t>
+        </is>
+      </c>
+      <c r="B286" s="5" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>قنا</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>قنا</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>نجع حمادي</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>دندرة</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>أبيدوس</t>
+        </is>
+      </c>
+      <c r="B290" s="4" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>قفطي</t>
+        </is>
+      </c>
+      <c r="B291" s="4" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>أخميم</t>
+        </is>
+      </c>
+      <c r="B292" s="4" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>سوهاج القديمة</t>
+        </is>
+      </c>
+      <c r="B293" s="4" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>النجع البحري</t>
+        </is>
+      </c>
+      <c r="B294" s="4" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>الشنقي</t>
+        </is>
+      </c>
+      <c r="B295" s="5" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>دسوق</t>
+        </is>
+      </c>
+      <c r="B297" s="4" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>بلامون</t>
+        </is>
+      </c>
+      <c r="B298" s="4" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>الرياض</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>سيدي سالم</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>الحامول</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>برج البرلس</t>
+        </is>
+      </c>
+      <c r="B302" s="4" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>مطوبس</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>المحمودية</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>بيلا</t>
+        </is>
+      </c>
+      <c r="B305" s="5" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>سيوه</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>السلوم</t>
+        </is>
+      </c>
+      <c r="B308" s="4" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>سيدي براني</t>
+        </is>
+      </c>
+      <c r="B309" s="4" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>العلمين</t>
+        </is>
+      </c>
+      <c r="B310" s="4" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>مارينا</t>
+        </is>
+      </c>
+      <c r="B311" s="4" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>توريدو</t>
+        </is>
+      </c>
+      <c r="B312" s="4" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>جنوب سيوه</t>
+        </is>
+      </c>
+      <c r="B313" s="4" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>شمال سيوه</t>
+        </is>
+      </c>
+      <c r="B314" s="4" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>كشته</t>
+        </is>
+      </c>
+      <c r="B315" s="5" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B23:B31"/>
+    <mergeCell ref="B84:B99"/>
+    <mergeCell ref="B306:B315"/>
+    <mergeCell ref="B152:B188"/>
+    <mergeCell ref="B142:B151"/>
+    <mergeCell ref="B287:B295"/>
+    <mergeCell ref="B236:B245"/>
+    <mergeCell ref="B261:B268"/>
+    <mergeCell ref="B204:B215"/>
+    <mergeCell ref="B296:B305"/>
+    <mergeCell ref="B59:B68"/>
+    <mergeCell ref="B246:B252"/>
+    <mergeCell ref="B121:B132"/>
+    <mergeCell ref="B133:B141"/>
+    <mergeCell ref="B269:B277"/>
+    <mergeCell ref="B216:B226"/>
+    <mergeCell ref="B32:B49"/>
+    <mergeCell ref="B253:B260"/>
+    <mergeCell ref="B69:B83"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B50:B58"/>
+    <mergeCell ref="B189:B203"/>
+    <mergeCell ref="B227:B235"/>
+    <mergeCell ref="B100:B112"/>
+    <mergeCell ref="B12:B22"/>
+    <mergeCell ref="B113:B120"/>
+    <mergeCell ref="B278:B286"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>